--- a/论文方案/实验结果.xlsx
+++ b/论文方案/实验结果.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\WH\论文方案\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\WPSDrive\668498707\WPS云盘\研二\论文2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>初始原型</t>
     </r>
     <r>
@@ -259,6 +265,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>仅</t>
     </r>
     <r>
@@ -283,6 +295,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>仅</t>
     </r>
     <r>
@@ -1107,7 +1125,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1162,10 +1180,13 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1750,7 +1771,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" ht="14.25" spans="1:13">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -2601,11 +2622,11 @@
         <v>47.28</v>
       </c>
       <c r="K23" s="17">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L23" s="17">
         <f>(2*J23*K23)/(J23+K23)</f>
-        <v>33.2237837837838</v>
+        <v>31.4933220482438</v>
       </c>
       <c r="M23" s="17">
         <v>23.96</v>
@@ -2652,7 +2673,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" ht="14.25" spans="1:13">
+    <row r="32" spans="1:13">
       <c r="A32" s="4"/>
       <c r="B32" s="5" t="s">
         <v>5</v>
@@ -2699,38 +2720,40 @@
         <v>19.26</v>
       </c>
       <c r="C33" s="11">
-        <v>10.28</v>
-      </c>
-      <c r="D33" s="11">
-        <v>13.41</v>
+        <v>9.28</v>
+      </c>
+      <c r="D33" s="12">
+        <f>(2*B33*C33)/(B33+C33)</f>
+        <v>12.525073580939</v>
       </c>
       <c r="E33" s="11">
         <v>9.86</v>
       </c>
       <c r="F33" s="11">
-        <v>44.17</v>
+        <v>40.17</v>
       </c>
       <c r="G33" s="11">
-        <v>42.37</v>
-      </c>
-      <c r="H33" s="11">
-        <v>43.25</v>
+        <v>35.37</v>
+      </c>
+      <c r="H33" s="12">
+        <f>(2*F33*G33)/(F33+G33)</f>
+        <v>37.6174980142971</v>
       </c>
       <c r="I33" s="11">
-        <v>46.27</v>
+        <v>37.27</v>
       </c>
       <c r="J33" s="11">
-        <v>12.36</v>
+        <v>20.36</v>
       </c>
       <c r="K33" s="11">
-        <v>20.33</v>
+        <v>16.33</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" ref="L33:L36" si="0">(2*J33*K33)/(J33+K33)</f>
-        <v>15.3734353013154</v>
+        <v>18.1236740256201</v>
       </c>
       <c r="M33" s="18">
-        <v>29.67</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2754,14 +2777,14 @@
         <v>30.76</v>
       </c>
       <c r="G34" s="11">
-        <v>37.52</v>
+        <v>22.52</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" ref="H34:H36" si="1">(2*F34*G34)/(F34+G34)</f>
-        <v>33.8053661394259</v>
+        <v>26.0028228228228</v>
       </c>
       <c r="I34" s="11">
-        <v>41.61</v>
+        <v>23.61</v>
       </c>
       <c r="J34" s="11">
         <v>29.71</v>
@@ -2774,7 +2797,7 @@
         <v>22.3946602348993</v>
       </c>
       <c r="M34" s="11">
-        <v>15.85</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2785,11 +2808,11 @@
         <v>24.23</v>
       </c>
       <c r="C35" s="18">
-        <v>19.56</v>
+        <v>9.56</v>
       </c>
       <c r="D35" s="12">
         <f>(2*B35*C35)/(B35+C35)</f>
-        <v>21.6459831011646</v>
+        <v>13.7104942290619</v>
       </c>
       <c r="E35" s="11">
         <v>10.66</v>
@@ -2811,11 +2834,11 @@
         <v>37.14</v>
       </c>
       <c r="K35" s="11">
-        <v>24.83</v>
+        <v>21.83</v>
       </c>
       <c r="L35" s="12">
         <f t="shared" si="0"/>
-        <v>29.762343069227</v>
+        <v>27.497581821265</v>
       </c>
       <c r="M35" s="11">
         <v>23.94</v>
@@ -2828,7 +2851,7 @@
       <c r="B36" s="19">
         <v>35.08</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="19">
         <v>16.87</v>
       </c>
       <c r="D36" s="19">
@@ -2854,13 +2877,13 @@
         <v>47.28</v>
       </c>
       <c r="K36" s="19">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L36" s="17">
         <f t="shared" si="0"/>
-        <v>33.2237837837838</v>
-      </c>
-      <c r="M36" s="20">
+        <v>31.4933220482438</v>
+      </c>
+      <c r="M36" s="19">
         <v>23.96</v>
       </c>
     </row>
@@ -2972,7 +2995,7 @@
         <v>47.5361703731625</v>
       </c>
       <c r="I42" s="11">
-        <v>47.88</v>
+        <v>42.88</v>
       </c>
       <c r="J42" s="11">
         <v>34.25</v>
@@ -3039,7 +3062,7 @@
       <c r="B44" s="11">
         <v>31.61</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="12">
         <v>11.3</v>
       </c>
       <c r="D44" s="12">
@@ -3053,26 +3076,26 @@
         <v>80.01</v>
       </c>
       <c r="G44" s="11">
-        <v>35.75</v>
+        <v>39.75</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="3"/>
-        <v>49.4187543192813</v>
-      </c>
-      <c r="I44" s="18">
+        <v>53.1128507014028</v>
+      </c>
+      <c r="I44" s="20">
         <v>50.67</v>
       </c>
       <c r="J44" s="11">
         <v>40.61</v>
       </c>
       <c r="K44" s="12">
-        <v>16.4</v>
+        <v>20.4</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="4"/>
-        <v>23.3644623750219</v>
-      </c>
-      <c r="M44" s="18">
+        <v>27.1576462874939</v>
+      </c>
+      <c r="M44" s="20">
         <v>24.43</v>
       </c>
     </row>
@@ -3083,7 +3106,7 @@
       <c r="B45" s="19">
         <v>35.08</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="21">
         <v>16.87</v>
       </c>
       <c r="D45" s="17">
@@ -3103,20 +3126,20 @@
         <f t="shared" si="3"/>
         <v>60.6291001056923</v>
       </c>
-      <c r="I45" s="20">
+      <c r="I45" s="21">
         <v>50.38</v>
       </c>
       <c r="J45" s="19">
         <v>47.28</v>
       </c>
       <c r="K45" s="19">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L45" s="17">
         <f t="shared" si="4"/>
-        <v>33.2237837837838</v>
-      </c>
-      <c r="M45" s="20">
+        <v>31.4933220482438</v>
+      </c>
+      <c r="M45" s="21">
         <v>23.96</v>
       </c>
     </row>
@@ -3228,7 +3251,7 @@
         <v>34.2660014531364</v>
       </c>
       <c r="I51" s="11">
-        <v>40.63</v>
+        <v>32.63</v>
       </c>
       <c r="J51" s="11">
         <v>33.06</v>
@@ -3252,11 +3275,11 @@
         <v>23.51</v>
       </c>
       <c r="C52" s="11">
-        <v>12.17</v>
+        <v>12.23</v>
       </c>
       <c r="D52" s="12">
         <f t="shared" si="5"/>
-        <v>16.0379316143498</v>
+        <v>16.089944040291</v>
       </c>
       <c r="E52" s="11">
         <v>12.23</v>
@@ -3265,11 +3288,11 @@
         <v>52.75</v>
       </c>
       <c r="G52" s="11">
-        <v>44.19</v>
+        <v>34.19</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="6"/>
-        <v>48.0920672580978</v>
+        <v>41.4889003910743</v>
       </c>
       <c r="I52" s="11">
         <v>35.19</v>
@@ -3322,11 +3345,11 @@
         <v>41.84</v>
       </c>
       <c r="K53" s="11">
-        <v>20.88</v>
+        <v>18.88</v>
       </c>
       <c r="L53" s="12">
         <f t="shared" si="7"/>
-        <v>27.8577551020408</v>
+        <v>26.0190777338603</v>
       </c>
       <c r="M53" s="11">
         <v>19.72</v>
@@ -3336,43 +3359,43 @@
       <c r="A54" s="11">
         <v>7</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="20">
         <v>35.08</v>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="20">
         <v>16.87</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54" s="22">
         <f t="shared" si="5"/>
         <v>22.7834302213667</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="20">
         <v>17.65</v>
       </c>
       <c r="F54" s="11">
         <v>85.49</v>
       </c>
-      <c r="G54" s="18">
+      <c r="G54" s="20">
         <v>46.97</v>
       </c>
-      <c r="H54" s="21">
+      <c r="H54" s="22">
         <f t="shared" si="6"/>
         <v>60.6291001056923</v>
       </c>
       <c r="I54" s="11">
         <v>50.38</v>
       </c>
-      <c r="J54" s="18">
+      <c r="J54" s="20">
         <v>47.28</v>
       </c>
-      <c r="K54" s="18">
-        <v>25.61</v>
-      </c>
-      <c r="L54" s="21">
+      <c r="K54" s="20">
+        <v>23.61</v>
+      </c>
+      <c r="L54" s="22">
         <f t="shared" si="7"/>
-        <v>33.2237837837838</v>
-      </c>
-      <c r="M54" s="18">
+        <v>31.4933220482438</v>
+      </c>
+      <c r="M54" s="20">
         <v>23.96</v>
       </c>
     </row>
@@ -3380,23 +3403,23 @@
       <c r="A55" s="15">
         <v>9</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="21">
         <v>30.99</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="21">
         <v>11.75</v>
       </c>
       <c r="D55" s="16">
         <f t="shared" si="5"/>
         <v>17.0394244267665</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="21">
         <v>14.73</v>
       </c>
       <c r="F55" s="19">
         <v>87.48</v>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="21">
         <v>45.77</v>
       </c>
       <c r="H55" s="16">
@@ -3406,17 +3429,17 @@
       <c r="I55" s="19">
         <v>51.48</v>
       </c>
-      <c r="J55" s="20">
+      <c r="J55" s="21">
         <v>43.97</v>
       </c>
-      <c r="K55" s="20">
-        <v>24.15</v>
+      <c r="K55" s="21">
+        <v>20.15</v>
       </c>
       <c r="L55" s="16">
         <f t="shared" si="7"/>
-        <v>31.1766147974163</v>
-      </c>
-      <c r="M55" s="20">
+        <v>27.6355427323768</v>
+      </c>
+      <c r="M55" s="21">
         <v>21.03</v>
       </c>
     </row>
@@ -3500,19 +3523,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" ht="32.25" spans="1:13">
-      <c r="A61" s="22" t="s">
+    <row r="61" ht="18.75" spans="1:13">
+      <c r="A61" s="23" t="s">
         <v>42</v>
       </c>
       <c r="B61" s="11">
         <v>13.48</v>
       </c>
       <c r="C61" s="11">
-        <v>11.13</v>
+        <v>10.13</v>
       </c>
       <c r="D61" s="12">
         <f t="shared" ref="D61:D64" si="8">(2*B61*C61)/(B61+C61)</f>
-        <v>12.1927996749289</v>
+        <v>11.5673358746294</v>
       </c>
       <c r="E61" s="11">
         <v>10.31</v>
@@ -3528,7 +3551,7 @@
         <v>34.806574237459</v>
       </c>
       <c r="I61" s="11">
-        <v>36.42</v>
+        <v>30.42</v>
       </c>
       <c r="J61" s="11">
         <v>28.31</v>
@@ -3545,7 +3568,7 @@
       </c>
     </row>
     <row r="62" ht="18.75" spans="1:13">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="23" t="s">
         <v>43</v>
       </c>
       <c r="B62" s="12">
@@ -3572,24 +3595,24 @@
         <v>48.3834079295154</v>
       </c>
       <c r="I62" s="11">
-        <v>49.26</v>
-      </c>
-      <c r="J62" s="21">
+        <v>41.26</v>
+      </c>
+      <c r="J62" s="22">
         <v>48.2</v>
       </c>
       <c r="K62" s="11">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="L62" s="12">
         <f t="shared" si="10"/>
-        <v>30.1164051355207</v>
+        <v>29.1571635311143</v>
       </c>
       <c r="M62" s="11">
         <v>21.35</v>
       </c>
     </row>
     <row r="63" ht="18.75" spans="1:13">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="23" t="s">
         <v>44</v>
       </c>
       <c r="B63" s="12">
@@ -3609,11 +3632,11 @@
         <v>74.08</v>
       </c>
       <c r="G63" s="12">
-        <v>46.9</v>
+        <v>43.9</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="9"/>
-        <v>57.4367994709869</v>
+        <v>55.1298864214274</v>
       </c>
       <c r="I63" s="11">
         <v>43.96</v>
@@ -3628,11 +3651,11 @@
         <f t="shared" si="10"/>
         <v>26.2575973908317</v>
       </c>
-      <c r="M63" s="18">
+      <c r="M63" s="20">
         <v>24.52</v>
       </c>
     </row>
-    <row r="64" ht="14.25" spans="1:13">
+    <row r="64" spans="1:13">
       <c r="A64" s="15" t="s">
         <v>45</v>
       </c>
@@ -3662,20 +3685,21 @@
       <c r="I64" s="19">
         <v>50.38</v>
       </c>
-      <c r="J64" s="20">
+      <c r="J64" s="21">
         <v>47.28</v>
       </c>
       <c r="K64" s="19">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L64" s="17">
         <f t="shared" si="10"/>
-        <v>33.2237837837838</v>
-      </c>
-      <c r="M64" s="20">
+        <v>31.4933220482438</v>
+      </c>
+      <c r="M64" s="21">
         <v>23.96</v>
       </c>
     </row>
+    <row r="65" ht="14.25"/>
     <row r="67" ht="14.25" spans="1:13">
       <c r="A67" s="1" t="s">
         <v>46</v>
@@ -3763,11 +3787,11 @@
         <v>19.87</v>
       </c>
       <c r="C70" s="11">
-        <v>11.45</v>
+        <v>10.45</v>
       </c>
       <c r="D70" s="12">
         <f t="shared" ref="D70:D73" si="11">(2*B70*C70)/(B70+C70)</f>
-        <v>14.5281928480204</v>
+        <v>13.6966688654354</v>
       </c>
       <c r="E70" s="11">
         <v>11.39</v>
@@ -3783,17 +3807,17 @@
         <v>38.45497818835</v>
       </c>
       <c r="I70" s="11">
-        <v>46.92</v>
+        <v>36.92</v>
       </c>
       <c r="J70" s="11">
         <v>24.47</v>
       </c>
       <c r="K70" s="11">
-        <v>17.15</v>
+        <v>12.15</v>
       </c>
       <c r="L70" s="12">
         <f t="shared" ref="L70:L73" si="13">(2*J70*K70)/(J70+K70)</f>
-        <v>20.1662902450745</v>
+        <v>16.2376024030584</v>
       </c>
       <c r="M70" s="11">
         <v>12.44</v>
@@ -3807,11 +3831,11 @@
         <v>24.03</v>
       </c>
       <c r="C71" s="11">
-        <v>12.63</v>
+        <v>9.63</v>
       </c>
       <c r="D71" s="12">
         <f t="shared" si="11"/>
-        <v>16.557495908347</v>
+        <v>13.7497860962567</v>
       </c>
       <c r="E71" s="11">
         <v>11.56</v>
@@ -3858,7 +3882,7 @@
         <v>9.75835051546392</v>
       </c>
       <c r="E72" s="11">
-        <v>10.02</v>
+        <v>9.02</v>
       </c>
       <c r="F72" s="11">
         <v>67.43</v>
@@ -3877,17 +3901,17 @@
         <v>35.21</v>
       </c>
       <c r="K72" s="11">
-        <v>22.59</v>
+        <v>16.59</v>
       </c>
       <c r="L72" s="12">
         <f t="shared" si="13"/>
-        <v>27.5222802768166</v>
+        <v>22.5534324324324</v>
       </c>
       <c r="M72" s="11">
         <v>20.74</v>
       </c>
     </row>
-    <row r="73" ht="14.25" spans="1:13">
+    <row r="73" spans="1:13">
       <c r="A73" s="15" t="s">
         <v>50</v>
       </c>
@@ -3921,11 +3945,11 @@
         <v>47.28</v>
       </c>
       <c r="K73" s="19">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L73" s="17">
         <f t="shared" si="13"/>
-        <v>33.2237837837838</v>
+        <v>31.4933220482438</v>
       </c>
       <c r="M73" s="19">
         <v>23.96</v>
@@ -4052,7 +4076,7 @@
         <v>20.0118865030675</v>
       </c>
       <c r="M79" s="11">
-        <v>21.51</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -4083,23 +4107,23 @@
         <v>40.4130792184041</v>
       </c>
       <c r="I80" s="11">
-        <v>41.47</v>
+        <v>34.47</v>
       </c>
       <c r="J80" s="11">
         <v>33.19</v>
       </c>
       <c r="K80" s="11">
-        <v>19.55</v>
+        <v>15.55</v>
       </c>
       <c r="L80" s="12">
         <f t="shared" si="16"/>
-        <v>24.6061623056504</v>
+        <v>21.1778621255642</v>
       </c>
       <c r="M80" s="11">
         <v>17.72</v>
       </c>
     </row>
-    <row r="81" ht="14.25" spans="1:13">
+    <row r="81" spans="1:13">
       <c r="A81" s="15" t="s">
         <v>55</v>
       </c>
@@ -4133,16 +4157,17 @@
         <v>47.28</v>
       </c>
       <c r="K81" s="19">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L81" s="17">
         <f t="shared" si="16"/>
-        <v>33.2237837837838</v>
+        <v>31.4933220482438</v>
       </c>
       <c r="M81" s="19">
         <v>23.96</v>
       </c>
     </row>
+    <row r="82" ht="14.25"/>
     <row r="84" ht="14.25" spans="1:13">
       <c r="A84" s="1" t="s">
         <v>56</v>
@@ -4280,7 +4305,7 @@
         <f t="shared" si="17"/>
         <v>19.0990647118301</v>
       </c>
-      <c r="E88" s="18">
+      <c r="E88" s="20">
         <v>18.06</v>
       </c>
       <c r="F88" s="11">
@@ -4300,11 +4325,11 @@
         <v>35.66</v>
       </c>
       <c r="K88" s="11">
-        <v>23.51</v>
+        <v>16.51</v>
       </c>
       <c r="L88" s="12">
         <f t="shared" si="19"/>
-        <v>28.3375561940172</v>
+        <v>22.5703124400997</v>
       </c>
       <c r="M88" s="11">
         <v>21.42</v>
@@ -4331,11 +4356,11 @@
         <v>53.69</v>
       </c>
       <c r="G89" s="11">
-        <v>36.06</v>
+        <v>32.06</v>
       </c>
       <c r="H89" s="12">
         <f t="shared" si="18"/>
-        <v>43.1434295264624</v>
+        <v>40.1469714285714</v>
       </c>
       <c r="I89" s="11">
         <v>34.93</v>
@@ -4351,10 +4376,10 @@
         <v>23.9466422317247</v>
       </c>
       <c r="M89" s="11">
-        <v>18.96</v>
-      </c>
-    </row>
-    <row r="90" ht="14.25" spans="1:13">
+        <v>20.96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="15" t="s">
         <v>55</v>
       </c>
@@ -4368,7 +4393,7 @@
         <f t="shared" si="17"/>
         <v>22.7834302213667</v>
       </c>
-      <c r="E90" s="20">
+      <c r="E90" s="21">
         <v>17.65</v>
       </c>
       <c r="F90" s="19">
@@ -4388,11 +4413,11 @@
         <v>47.28</v>
       </c>
       <c r="K90" s="19">
-        <v>25.61</v>
+        <v>23.61</v>
       </c>
       <c r="L90" s="17">
         <f t="shared" si="19"/>
-        <v>33.2237837837838</v>
+        <v>31.4933220482438</v>
       </c>
       <c r="M90" s="19">
         <v>23.96</v>

--- a/论文方案/实验结果.xlsx
+++ b/论文方案/实验结果.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\WPSDrive\668498707\WPS云盘\研二\论文2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\WH\论文方案\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -584,19 +584,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <vertAlign val="superscript"/>
@@ -613,7 +600,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -2673,7 +2673,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" ht="14.25" spans="1:13">
       <c r="A32" s="4"/>
       <c r="B32" s="5" t="s">
         <v>5</v>
@@ -3528,43 +3528,43 @@
         <v>42</v>
       </c>
       <c r="B61" s="11">
-        <v>13.48</v>
+        <v>19.26</v>
       </c>
       <c r="C61" s="11">
-        <v>10.13</v>
+        <v>9.28</v>
       </c>
       <c r="D61" s="12">
-        <f t="shared" ref="D61:D64" si="8">(2*B61*C61)/(B61+C61)</f>
-        <v>11.5673358746294</v>
+        <f>(2*B61*C61)/(B61+C61)</f>
+        <v>12.525073580939</v>
       </c>
       <c r="E61" s="11">
-        <v>10.31</v>
+        <v>9.86</v>
       </c>
       <c r="F61" s="11">
-        <v>53.56</v>
+        <v>40.17</v>
       </c>
       <c r="G61" s="11">
-        <v>25.78</v>
+        <v>35.37</v>
       </c>
       <c r="H61" s="12">
-        <f t="shared" ref="H61:H64" si="9">(2*F61*G61)/(F61+G61)</f>
-        <v>34.806574237459</v>
+        <f>(2*F61*G61)/(F61+G61)</f>
+        <v>37.6174980142971</v>
       </c>
       <c r="I61" s="11">
-        <v>30.42</v>
+        <v>37.27</v>
       </c>
       <c r="J61" s="11">
-        <v>28.31</v>
+        <v>20.36</v>
       </c>
       <c r="K61" s="11">
-        <v>16.77</v>
+        <v>16.33</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" ref="L61:L64" si="10">(2*J61*K61)/(J61+K61)</f>
-        <v>21.0629414374445</v>
-      </c>
-      <c r="M61" s="11">
-        <v>17.07</v>
+        <f>(2*J61*K61)/(J61+K61)</f>
+        <v>18.1236740256201</v>
+      </c>
+      <c r="M61" s="18">
+        <v>17.67</v>
       </c>
     </row>
     <row r="62" ht="18.75" spans="1:13">
@@ -3578,7 +3578,7 @@
         <v>12.95</v>
       </c>
       <c r="D62" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D61:D64" si="8">(2*B62*C62)/(B62+C62)</f>
         <v>16.9439252336449</v>
       </c>
       <c r="E62" s="11">
@@ -3591,7 +3591,7 @@
         <v>34.96</v>
       </c>
       <c r="H62" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H61:H64" si="9">(2*F62*G62)/(F62+G62)</f>
         <v>48.3834079295154</v>
       </c>
       <c r="I62" s="11">
@@ -3604,7 +3604,7 @@
         <v>20.9</v>
       </c>
       <c r="L62" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="L61:L64" si="10">(2*J62*K62)/(J62+K62)</f>
         <v>29.1571635311143</v>
       </c>
       <c r="M62" s="11">
@@ -3655,7 +3655,7 @@
         <v>24.52</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" ht="14.25" spans="1:13">
       <c r="A64" s="15" t="s">
         <v>45</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>20.74</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" ht="14.25" spans="1:13">
       <c r="A73" s="15" t="s">
         <v>50</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" ht="14.25" spans="1:13">
       <c r="A81" s="15" t="s">
         <v>55</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>20.96</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" ht="14.25" spans="1:13">
       <c r="A90" s="15" t="s">
         <v>55</v>
       </c>
